--- a/3DCard/Assets/Editor/ExcelToSO/配置表.xlsx
+++ b/3DCard/Assets/Editor/ExcelToSO/配置表.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="22420" windowHeight="12080" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="卡牌配置" sheetId="1" r:id="rId1"/>
-    <sheet name="可交互物体编号" sheetId="3" r:id="rId2"/>
+    <sheet name="合成表" sheetId="3" r:id="rId2"/>
     <sheet name="手牌交互组合" sheetId="2" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
   <si>
     <t>卡牌名称</t>
   </si>
@@ -44,94 +44,250 @@
     <t>卡牌类型</t>
   </si>
   <si>
+    <t>values</t>
+  </si>
+  <si>
     <t>卡牌描述</t>
   </si>
   <si>
+    <t>木头</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>E_Entity</t>
+  </si>
+  <si>
     <t>石头</t>
   </si>
   <si>
     <t>Rock</t>
   </si>
   <si>
-    <t>E_Entity</t>
+    <t>无用之石</t>
+  </si>
+  <si>
+    <t>铁</t>
+  </si>
+  <si>
+    <t>Iron</t>
+  </si>
+  <si>
+    <t>皮革</t>
+  </si>
+  <si>
+    <t>Leather</t>
+  </si>
+  <si>
+    <t>草</t>
+  </si>
+  <si>
+    <t>Grass</t>
+  </si>
+  <si>
+    <t>绳子</t>
+  </si>
+  <si>
+    <t>Rope</t>
+  </si>
+  <si>
+    <t>火</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>刹那即逝的火花</t>
+  </si>
+  <si>
+    <t>营火</t>
+  </si>
+  <si>
+    <t>Campfire</t>
+  </si>
+  <si>
+    <t>木剑</t>
+  </si>
+  <si>
+    <t>WoodSword</t>
+  </si>
+  <si>
+    <t>石剑</t>
+  </si>
+  <si>
+    <t>StoneSword</t>
+  </si>
+  <si>
+    <t>铁剑</t>
+  </si>
+  <si>
+    <t>IronSword</t>
+  </si>
+  <si>
+    <t>木盾</t>
+  </si>
+  <si>
+    <t>WoodShield</t>
+  </si>
+  <si>
+    <t>石盾</t>
+  </si>
+  <si>
+    <t>RockShield</t>
+  </si>
+  <si>
+    <t>铁盾</t>
+  </si>
+  <si>
+    <t>IronShield</t>
+  </si>
+  <si>
+    <t>草鞋</t>
+  </si>
+  <si>
+    <t>StrawSandals</t>
+  </si>
+  <si>
+    <t>皮革鞋</t>
+  </si>
+  <si>
+    <t>LeatherShoes</t>
+  </si>
+  <si>
+    <t>铁靴</t>
+  </si>
+  <si>
+    <t>IronBoots</t>
+  </si>
+  <si>
+    <t>打击</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>E_Behavior</t>
+  </si>
+  <si>
+    <t>100,1</t>
+  </si>
+  <si>
+    <t>造成伤害</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>Defend</t>
+  </si>
+  <si>
+    <t>拆解</t>
+  </si>
+  <si>
+    <t>Dismantle</t>
+  </si>
+  <si>
+    <t>组合</t>
+  </si>
+  <si>
+    <t>生成卡牌</t>
+  </si>
+  <si>
+    <t>组合id</t>
+  </si>
+  <si>
+    <t>优先级</t>
+  </si>
+  <si>
+    <t>解释</t>
+  </si>
+  <si>
+    <t>草_2</t>
+  </si>
+  <si>
+    <t>木头_3</t>
+  </si>
+  <si>
+    <t>木头_2,绳子_1</t>
+  </si>
+  <si>
+    <t>绳子_1,草_1</t>
+  </si>
+  <si>
+    <t>木头_1,石头_2</t>
+  </si>
+  <si>
+    <t>石头_2,绳子_1</t>
+  </si>
+  <si>
+    <t>绳子_1,皮革_1</t>
+  </si>
+  <si>
+    <t>铁_2,木头_1</t>
+  </si>
+  <si>
+    <t>铁_2,皮革_1</t>
+  </si>
+  <si>
+    <t>铁_1,绳子_1,皮革_1</t>
+  </si>
+  <si>
+    <t>火_1,石头_1,木头_1</t>
+  </si>
+  <si>
+    <t>DragedCard_ID</t>
+  </si>
+  <si>
+    <t>SelectedCard_ID</t>
+  </si>
+  <si>
+    <t>PointInteractableObj_ID</t>
+  </si>
+  <si>
+    <t>Func_ID</t>
+  </si>
+  <si>
+    <t>0_空</t>
+  </si>
+  <si>
+    <t>1_石头</t>
+  </si>
+  <si>
+    <t>10002_桌子</t>
+  </si>
+  <si>
+    <t>1_放下卡牌手牌到桌子上</t>
+  </si>
+  <si>
+    <t>2001_打击</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>Null</t>
+  </si>
+  <si>
+    <t>空</t>
   </si>
   <si>
     <t>Ek = 1/2mv^2</t>
   </si>
   <si>
-    <t>打击</t>
-  </si>
-  <si>
-    <t>Attack</t>
-  </si>
-  <si>
-    <t>E_Behavior</t>
+    <t>循环</t>
+  </si>
+  <si>
+    <t>Circulate</t>
+  </si>
+  <si>
+    <t>E_Modificatory</t>
+  </si>
+  <si>
+    <t>打出的卡牌不会消耗</t>
   </si>
   <si>
     <t>造成x点物理伤害</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Null</t>
-  </si>
-  <si>
-    <t>Boss</t>
-  </si>
-  <si>
-    <t>Table</t>
-  </si>
-  <si>
-    <t>Door</t>
-  </si>
-  <si>
-    <t>DragedCard_ID</t>
-  </si>
-  <si>
-    <t>SelectedCard_ID</t>
-  </si>
-  <si>
-    <t>PointInteractableObj_ID</t>
-  </si>
-  <si>
-    <t>Func_ID</t>
-  </si>
-  <si>
-    <t>0_空</t>
-  </si>
-  <si>
-    <t>1_石头</t>
-  </si>
-  <si>
-    <t>10002_桌子</t>
-  </si>
-  <si>
-    <t>1_放下卡牌手牌到桌子上</t>
-  </si>
-  <si>
-    <t>2001_打击</t>
-  </si>
-  <si>
-    <t>null</t>
-  </si>
-  <si>
-    <t>空</t>
-  </si>
-  <si>
-    <t>循环</t>
-  </si>
-  <si>
-    <t>Circulate</t>
-  </si>
-  <si>
-    <t>E_Modificatory</t>
-  </si>
-  <si>
-    <t>打出的卡牌不会消耗</t>
   </si>
   <si>
     <t>投掷</t>
@@ -1097,16 +1253,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="18.25" customWidth="1"/>
     <col min="3" max="3" width="14.85" style="3" customWidth="1"/>
     <col min="4" max="4" width="14.0333333333333" customWidth="1"/>
-    <col min="5" max="5" width="20.25" customWidth="1"/>
+    <col min="5" max="5" width="15.8583333333333" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.7333333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1119,55 +1276,325 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1">
         <v>7</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+      <c r="F8" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1">
         <v>10</v>
       </c>
-      <c r="C3" s="3">
-        <v>2001</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="1">
         <v>11</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="3:3">
-      <c r="C4"/>
-    </row>
-    <row r="5" spans="3:3">
-      <c r="C5"/>
-    </row>
-    <row r="6" spans="3:3">
-      <c r="C6"/>
-    </row>
-    <row r="7" spans="3:3">
-      <c r="C7"/>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1">
+        <v>13</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="1">
+        <v>14</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="1">
+        <v>15</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="1">
+        <v>16</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="2"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="1">
+        <v>17</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1001</v>
+      </c>
+      <c r="D19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1002</v>
+      </c>
+      <c r="D20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F20" s="2"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="3">
+        <v>1003</v>
+      </c>
+      <c r="D21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="3">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1178,52 +1605,194 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="1"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="14.15" style="3" customWidth="1"/>
+    <col min="1" max="1" width="17.1083333333333" style="3" customWidth="1"/>
     <col min="2" max="16384" width="8.66666666666667" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="3">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="3">
-        <v>10002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="3" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3">
-        <v>10003</v>
-      </c>
+      <c r="C2" s="3">
+        <v>11001</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="3">
+        <v>11002</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="E3"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="3">
+        <v>11003</v>
+      </c>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3">
+        <v>11004</v>
+      </c>
+      <c r="D5" s="3">
+        <v>4</v>
+      </c>
+      <c r="E5"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="3">
+        <v>11005</v>
+      </c>
+      <c r="D6" s="3">
+        <v>5</v>
+      </c>
+      <c r="E6"/>
+    </row>
+    <row r="7" customHeight="1" spans="1:5">
+      <c r="A7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="3">
+        <v>11006</v>
+      </c>
+      <c r="D7" s="3">
+        <v>6</v>
+      </c>
+      <c r="E7"/>
+    </row>
+    <row r="8" customHeight="1" spans="1:5">
+      <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="3">
+        <v>11007</v>
+      </c>
+      <c r="D8" s="3">
+        <v>7</v>
+      </c>
+      <c r="E8"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="3">
+        <v>11008</v>
+      </c>
+      <c r="D9" s="3">
+        <v>8</v>
+      </c>
+      <c r="E9"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="3">
+        <v>11009</v>
+      </c>
+      <c r="D10" s="3">
+        <v>9</v>
+      </c>
+      <c r="E10"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="3">
+        <v>11010</v>
+      </c>
+      <c r="D11" s="3">
+        <v>10</v>
+      </c>
+      <c r="E11"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="3">
+        <v>11011</v>
+      </c>
+      <c r="D12" s="3">
+        <v>11</v>
+      </c>
+      <c r="E12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1245,38 +1814,38 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="C1" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="D1" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" s="3" customFormat="1" spans="1:4">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" s="3" customFormat="1" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="1"/>
@@ -1340,109 +1909,109 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="C2" s="1">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="C4" s="3">
         <v>1001</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C5" s="3">
         <v>2001</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="C6" s="3">
         <v>2002</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>12</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="C7" s="3">
         <v>3001</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
